--- a/Data IKPA KPPN/2026/IKPA_KPPN_MARET_2026.xlsx
+++ b/Data IKPA KPPN/2026/IKPA_KPPN_MARET_2026.xlsx
@@ -584,8 +584,10 @@
           <t>MARET</t>
         </is>
       </c>
-      <c r="O2" t="n">
-        <v>2026</v>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>

--- a/Data IKPA KPPN/2026/IKPA_KPPN_MARET_2026.xlsx
+++ b/Data IKPA KPPN/2026/IKPA_KPPN_MARET_2026.xlsx
@@ -425,176 +425,186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Kode KPPN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nama KPPN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Kualitas Perencanaan Anggaran</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kualitas Pelaksanaan Anggaran</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Kualitas Hasil Pelaksanaan Anggaran</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Revisi DIPA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Deviasi Halaman III DIPA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Penyerapan Anggaran</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Belanja Kontraktual</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Penyelesaian Tagihan</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Pengelolaan UP dan TUP</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Capaian Output</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nilai Total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Konversi Bobot</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Dispensasi SPM (Pengurangan)</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Dispensasi SPM (Pengurang)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Nilai Akhir (Nilai Total/Konversi Bobot)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Bulan</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Tahun</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Peringkat</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>BATURAJA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>100,00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>100,00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>100,00</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>100,00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>100,00</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100,00</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>75,13</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>100,00%</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" t="n">
+        <v>100</v>
       </c>
       <c r="M2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N2" t="n">
+        <v>75.13</v>
+      </c>
+      <c r="O2" t="n">
+        <v>100</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>75.13</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>MARET</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="T2" t="inlineStr">
         <is>
           <t>Upload</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="U2" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Data IKPA KPPN/2026/IKPA_KPPN_MARET_2026.xlsx
+++ b/Data IKPA KPPN/2026/IKPA_KPPN_MARET_2026.xlsx
@@ -556,7 +556,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>0.51</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -577,10 +577,10 @@
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>0.51</v>
+        <v>100</v>
       </c>
       <c r="N2" t="n">
-        <v>75.13</v>
+        <v>100</v>
       </c>
       <c r="O2" t="n">
         <v>100</v>
@@ -589,7 +589,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>75.13</v>
+        <v>100</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>

--- a/Data IKPA KPPN/2026/IKPA_KPPN_MARET_2026.xlsx
+++ b/Data IKPA KPPN/2026/IKPA_KPPN_MARET_2026.xlsx
@@ -556,7 +556,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>0.51</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -577,10 +577,10 @@
         <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>100</v>
+        <v>0.51</v>
       </c>
       <c r="N2" t="n">
-        <v>100</v>
+        <v>75.13</v>
       </c>
       <c r="O2" t="n">
         <v>100</v>
@@ -589,7 +589,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>100</v>
+        <v>75.13</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
